--- a/app/templates/report/ltc.xlsx
+++ b/app/templates/report/ltc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32DD4E2-44F2-4A34-82D2-91F2753C5D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762642CE-F5E2-4E28-8F37-A146D37CDC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="LTC" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LTC!$A$3:$AH$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LTC!$A$3:$AI$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Edificio</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Customer</t>
+  </si>
+  <si>
+    <t>Type of contract</t>
   </si>
 </sst>
 </file>
@@ -742,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -757,19 +760,19 @@
     <col min="10" max="10" width="12.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="5.7109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="18.85546875" style="1" customWidth="1"/>
-    <col min="13" max="15" width="12.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="15.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" style="1" customWidth="1"/>
-    <col min="23" max="26" width="15.42578125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="22.42578125" style="1" customWidth="1"/>
-    <col min="28" max="34" width="15.42578125" style="1" customWidth="1"/>
-    <col min="35" max="16384" width="14.42578125" style="1"/>
+    <col min="13" max="16" width="12.28515625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="15.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" style="1" customWidth="1"/>
+    <col min="24" max="27" width="15.42578125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="22.42578125" style="1" customWidth="1"/>
+    <col min="29" max="35" width="15.42578125" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="14.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -800,10 +803,7 @@
       <c r="P1" s="17"/>
       <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
-      <c r="S1" s="19">
-        <f>SUBTOTAL(9,S4:S99999)</f>
-        <v>0</v>
-      </c>
+      <c r="S1" s="17"/>
       <c r="T1" s="19">
         <f>SUBTOTAL(9,T4:T99999)</f>
         <v>0</v>
@@ -812,21 +812,21 @@
         <f>SUBTOTAL(9,U4:U99999)</f>
         <v>0</v>
       </c>
-      <c r="V1" s="17"/>
-      <c r="W1" s="19">
-        <f t="shared" ref="W1:AG1" si="0">SUBTOTAL(9,W4:W99999)</f>
-        <v>0</v>
-      </c>
+      <c r="V1" s="19">
+        <f>SUBTOTAL(9,V4:V99999)</f>
+        <v>0</v>
+      </c>
+      <c r="W1" s="17"/>
       <c r="X1" s="19">
+        <f t="shared" ref="X1:AH1" si="0">SUBTOTAL(9,X4:X99999)</f>
+        <v>0</v>
+      </c>
+      <c r="Y1" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y1" s="19">
-        <f t="shared" ref="Y1" si="1">SUBTOTAL(9,Y4:Y99999)</f>
-        <v>0</v>
-      </c>
       <c r="Z1" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Z1" si="1">SUBTOTAL(9,Z4:Z99999)</f>
         <v>0</v>
       </c>
       <c r="AA1" s="19">
@@ -857,9 +857,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH1" s="19"/>
+      <c r="AH1" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI1" s="19"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
@@ -880,34 +884,35 @@
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="22"/>
+      <c r="R2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="21"/>
       <c r="S2" s="21"/>
       <c r="T2" s="21"/>
       <c r="U2" s="21"/>
       <c r="V2" s="21"/>
-      <c r="W2" s="22" t="s">
+      <c r="W2" s="21"/>
+      <c r="X2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="X2" s="22"/>
       <c r="Y2" s="22"/>
       <c r="Z2" s="22"/>
       <c r="AA2" s="22"/>
-      <c r="AB2" s="21" t="s">
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AC2" s="21"/>
       <c r="AD2" s="21"/>
-      <c r="AE2" s="22" t="s">
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="AF2" s="22"/>
       <c r="AG2" s="22"/>
       <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
     </row>
-    <row r="3" spans="1:34" s="6" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" s="6" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -954,64 +959,67 @@
         <v>29</v>
       </c>
       <c r="P3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="14" t="s">
+      <c r="X3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="X3" s="14" t="s">
+      <c r="Y3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="Y3" s="14" t="s">
+      <c r="Z3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="AA3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="AA3" s="14" t="s">
+      <c r="AB3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AD3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AE3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="14" t="s">
+      <c r="AF3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="AF3" s="14" t="s">
+      <c r="AG3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AH3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AH3" s="14" t="s">
+      <c r="AI3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1036,51 +1044,52 @@
         <v>26</v>
       </c>
       <c r="O4" s="20"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="10"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="12"/>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
-      <c r="V4" s="7" t="s">
+      <c r="V4" s="10"/>
+      <c r="W4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
-      <c r="Z4" s="10">
-        <f>X4-W4</f>
-        <v>0</v>
-      </c>
+      <c r="Z4" s="10"/>
       <c r="AA4" s="10">
-        <f>Z4-S4</f>
-        <v>0</v>
-      </c>
-      <c r="AB4" s="10"/>
+        <f>Y4-X4</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="10">
+        <f>AA4-T4</f>
+        <v>0</v>
+      </c>
       <c r="AC4" s="10"/>
-      <c r="AD4" s="10">
-        <f>AC4-AB4-S4</f>
-        <v>0</v>
-      </c>
+      <c r="AD4" s="10"/>
       <c r="AE4" s="10">
-        <f>AB4+S4</f>
+        <f>AD4-AC4-T4</f>
         <v>0</v>
       </c>
       <c r="AF4" s="10">
-        <f>AC4-W4</f>
+        <f>AC4+T4</f>
         <v>0</v>
       </c>
       <c r="AG4" s="10">
-        <f>AF4-AE4</f>
-        <v>0</v>
-      </c>
-      <c r="AH4" s="15">
-        <f>IF(AE4,AF4/AE4,0)</f>
+        <f>AD4-X4</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="10">
+        <f>AG4-AF4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="15">
+        <f>IF(AF4,AG4/AF4,0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AH4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AI4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
